--- a/Result/profitability/3313.xlsx
+++ b/Result/profitability/3313.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-1.59</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.27375</v>
+        <v>-0.2750000000000001</v>
       </c>
       <c r="N2" t="n">
-        <v>-78.05499999999999</v>
+        <v>-72.26000000000001</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-3.3</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.6737500000000001</v>
+        <v>-0.66</v>
       </c>
       <c r="N3" t="n">
-        <v>-78.40000000000001</v>
+        <v>-74.18124999999999</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.24</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4912500000000001</v>
+        <v>-0.495</v>
       </c>
       <c r="N4" t="n">
-        <v>-79.08</v>
+        <v>-55.63125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -914,13 +914,13 @@
         <v>1</v>
       </c>
       <c r="R4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.54</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.5487500000000001</v>
+        <v>-0.5425</v>
       </c>
       <c r="N5" t="n">
-        <v>-62.3775</v>
+        <v>-10.0975</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,16 +1137,16 @@
         <v>-1.84</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.75875</v>
+        <v>-0.7650000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-17.10625</v>
+        <v>-8.75</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.48</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.81125</v>
+        <v>-0.8187500000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>-14.21</v>
+        <v>1.08125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,16 +1391,16 @@
         <v>-0.77</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.90125</v>
+        <v>-0.9237500000000001</v>
       </c>
       <c r="N8" t="n">
-        <v>-4.155</v>
+        <v>7.38875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T8" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
         <v>-0.34</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.9187500000000001</v>
+        <v>-0.91875</v>
       </c>
       <c r="N10" t="n">
         <v>2.86625</v>
@@ -1772,7 +1772,7 @@
         <v>1.48</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3212500000000001</v>
+        <v>-0.32125</v>
       </c>
       <c r="N11" t="n">
         <v>4.80625</v>
@@ -9834,6 +9834,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3313</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>14</v>
+      </c>
+      <c r="D75" t="n">
+        <v>7</v>
+      </c>
+      <c r="E75" t="n">
+        <v>7</v>
+      </c>
+      <c r="F75" t="n">
+        <v>47.93</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-40.27%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-19</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-24</v>
+      </c>
+      <c r="K75" t="n">
+        <v>-24</v>
+      </c>
+      <c r="L75" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="M75" t="n">
+        <v>-0.08875000000000006</v>
+      </c>
+      <c r="N75" t="n">
+        <v>-73.00375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-0.18</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-2.571428571428571</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>92.34999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-2.079018460153084</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-0.3125</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>418.24</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-1.129432097431881</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
